--- a/AAII_Financials/Quarterly/ATVK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATVK_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
   <si>
     <t>ATVK</t>
   </si>
@@ -664,10 +664,11 @@
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -703,16 +704,16 @@
         <v>45016</v>
       </c>
       <c r="G7" s="2">
+        <v>44834</v>
+      </c>
+      <c r="H7" s="2">
+        <v>44742</v>
+      </c>
+      <c r="I7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44377</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44286</v>
-      </c>
-      <c r="J7" s="2">
-        <v>43524</v>
       </c>
       <c r="K7" s="2">
         <v>43434</v>
@@ -768,10 +769,10 @@
         <v>200</v>
       </c>
       <c r="I8" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -1082,14 +1083,14 @@
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>-800</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
@@ -1142,13 +1143,13 @@
         <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>4</v>
@@ -1218,16 +1219,16 @@
         <v>200</v>
       </c>
       <c r="G17" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="H17" s="3">
+        <v>500</v>
+      </c>
+      <c r="I17" s="3">
+        <v>600</v>
+      </c>
+      <c r="J17" s="3">
         <v>-500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>300</v>
-      </c>
-      <c r="J17" s="3">
-        <v>100</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -1277,16 +1278,16 @@
         <v>0</v>
       </c>
       <c r="G18" s="3">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="H18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J18" s="3">
         <v>700</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-100</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -1349,8 +1350,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1359,13 +1360,13 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1408,8 +1409,8 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>0</v>
       </c>
       <c r="E21" s="3">
         <v>0</v>
@@ -1418,13 +1419,13 @@
         <v>100</v>
       </c>
       <c r="G21" s="3">
-        <v>300</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="H21" s="3">
+        <v>200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>100</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>4</v>
@@ -1480,13 +1481,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>4</v>
@@ -1526,8 +1527,8 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>4</v>
+      <c r="D23" s="3">
+        <v>0</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
@@ -1536,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="G23" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>700</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-100</v>
       </c>
       <c r="K23" s="3">
         <v>-100</v>
@@ -1703,8 +1704,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>0</v>
       </c>
       <c r="E26" s="3">
         <v>0</v>
@@ -1713,16 +1714,16 @@
         <v>0</v>
       </c>
       <c r="G26" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>700</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-100</v>
       </c>
       <c r="K26" s="3">
         <v>-100</v>
@@ -1762,8 +1763,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>0</v>
       </c>
       <c r="E27" s="3">
         <v>0</v>
@@ -1772,16 +1773,16 @@
         <v>0</v>
       </c>
       <c r="G27" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>700</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-100</v>
       </c>
       <c r="K27" s="3">
         <v>-100</v>
@@ -2057,8 +2058,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2067,13 +2068,13 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -2116,8 +2117,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>0</v>
       </c>
       <c r="E33" s="3">
         <v>0</v>
@@ -2126,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="G33" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>700</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-100</v>
       </c>
       <c r="K33" s="3">
         <v>-100</v>
@@ -2234,8 +2235,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>0</v>
       </c>
       <c r="E35" s="3">
         <v>0</v>
@@ -2244,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="G35" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>700</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-100</v>
       </c>
       <c r="K35" s="3">
         <v>-100</v>
@@ -2308,16 +2309,16 @@
         <v>45016</v>
       </c>
       <c r="G38" s="2">
+        <v>44834</v>
+      </c>
+      <c r="H38" s="2">
+        <v>44742</v>
+      </c>
+      <c r="I38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44377</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44286</v>
-      </c>
-      <c r="J38" s="2">
-        <v>43524</v>
       </c>
       <c r="K38" s="2">
         <v>43434</v>
@@ -2816,8 +2817,8 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>4</v>
+      <c r="D48" s="3">
+        <v>0</v>
       </c>
       <c r="E48" s="3">
         <v>0</v>
@@ -4493,16 +4494,16 @@
         <v>45016</v>
       </c>
       <c r="G80" s="2">
+        <v>44834</v>
+      </c>
+      <c r="H80" s="2">
+        <v>44742</v>
+      </c>
+      <c r="I80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44377</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44286</v>
-      </c>
-      <c r="J80" s="2">
-        <v>43524</v>
       </c>
       <c r="K80" s="2">
         <v>43434</v>
@@ -4542,8 +4543,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>0</v>
       </c>
       <c r="E81" s="3">
         <v>0</v>
@@ -4552,16 +4553,16 @@
         <v>0</v>
       </c>
       <c r="G81" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>700</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-100</v>
       </c>
       <c r="K81" s="3">
         <v>-100</v>
@@ -4634,13 +4635,13 @@
         <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>100</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>4</v>
@@ -4993,11 +4994,11 @@
       <c r="H89" s="3">
         <v>100</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>4</v>
+      <c r="I89" s="3">
+        <v>100</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -5250,13 +5251,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -5568,10 +5569,10 @@
         <v>-100</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
+        <v>-100</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-100</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
@@ -5683,13 +5684,13 @@
         <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>4</v>
+      <c r="I102" s="3">
+        <v>100</v>
       </c>
       <c r="J102" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/ATVK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATVK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
   <si>
     <t>ATVK</t>
   </si>
@@ -656,100 +656,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44377</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>43434</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43343</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43251</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43159</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43069</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>42978</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>42886</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>42794</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42704</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42613</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42521</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -757,29 +763,29 @@
         <v>200</v>
       </c>
       <c r="E8" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F8" s="3">
         <v>200</v>
       </c>
       <c r="G8" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="H8" s="3">
         <v>200</v>
       </c>
       <c r="I8" s="3">
+        <v>300</v>
+      </c>
+      <c r="J8" s="3">
+        <v>600</v>
+      </c>
+      <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
         <v>0</v>
       </c>
@@ -807,8 +813,14 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -866,8 +878,14 @@
       <c r="U9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -925,8 +943,14 @@
       <c r="U10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -948,8 +972,10 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1007,8 +1033,14 @@
       <c r="U12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1066,8 +1098,14 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1089,26 +1127,26 @@
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>-800</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1125,8 +1163,14 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1137,10 +1181,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
@@ -1149,22 +1193,22 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="K15" s="3">
+        <v>100</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1184,8 +1228,14 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1204,8 +1254,10 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1213,38 +1265,38 @@
         <v>200</v>
       </c>
       <c r="E17" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F17" s="3">
         <v>200</v>
       </c>
       <c r="G17" s="3">
+        <v>300</v>
+      </c>
+      <c r="H17" s="3">
+        <v>200</v>
+      </c>
+      <c r="I17" s="3">
+        <v>200</v>
+      </c>
+      <c r="J17" s="3">
         <v>700</v>
       </c>
-      <c r="H17" s="3">
-        <v>500</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>-500</v>
       </c>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3">
-        <v>100</v>
-      </c>
       <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>100</v>
+      </c>
+      <c r="O17" s="3">
         <v>200</v>
       </c>
-      <c r="N17" s="3">
-        <v>100</v>
-      </c>
-      <c r="O17" s="3">
-        <v>0</v>
-      </c>
       <c r="P17" s="3">
         <v>100</v>
       </c>
@@ -1252,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="R17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17" s="3">
         <v>0</v>
@@ -1263,8 +1315,14 @@
       <c r="U17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3">
+        <v>0</v>
+      </c>
+      <c r="W17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1278,31 +1336,31 @@
         <v>0</v>
       </c>
       <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>100</v>
+      </c>
+      <c r="J18" s="3">
         <v>-100</v>
       </c>
-      <c r="H18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>700</v>
       </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-100</v>
-      </c>
       <c r="M18" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="N18" s="3">
         <v>-100</v>
       </c>
       <c r="O18" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="P18" s="3">
         <v>-100</v>
@@ -1311,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="R18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S18" s="3">
         <v>0</v>
@@ -1322,8 +1380,14 @@
       <c r="U18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1345,8 +1409,10 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1360,32 +1426,32 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
         <v>100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20" s="3">
+        <v>100</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1404,34 +1470,40 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I21" s="3">
-        <v>100</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
+        <v>300</v>
+      </c>
+      <c r="J21" s="3">
+        <v>100</v>
+      </c>
+      <c r="K21" s="3">
+        <v>100</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
@@ -1463,8 +1535,14 @@
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1472,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1481,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -1489,11 +1567,11 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>4</v>
@@ -1501,11 +1579,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1522,8 +1600,14 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1543,25 +1627,25 @@
         <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
         <v>700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-100</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-400</v>
       </c>
       <c r="N23" s="3">
         <v>-100</v>
       </c>
       <c r="O23" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="P23" s="3">
         <v>-100</v>
@@ -1570,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="R23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S23" s="3">
         <v>0</v>
@@ -1581,8 +1665,14 @@
       <c r="U23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1640,8 +1730,14 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1699,8 +1795,14 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1720,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
         <v>700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-100</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-400</v>
       </c>
       <c r="N26" s="3">
         <v>-100</v>
       </c>
       <c r="O26" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="P26" s="3">
         <v>-100</v>
@@ -1747,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="R26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S26" s="3">
         <v>0</v>
@@ -1758,8 +1860,14 @@
       <c r="U26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1779,25 +1887,25 @@
         <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
         <v>700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-100</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-400</v>
       </c>
       <c r="N27" s="3">
         <v>-100</v>
       </c>
       <c r="O27" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="P27" s="3">
         <v>-100</v>
@@ -1806,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="R27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S27" s="3">
         <v>0</v>
@@ -1817,8 +1925,14 @@
       <c r="U27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1876,8 +1990,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1935,8 +2055,14 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1994,8 +2120,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2053,8 +2185,14 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2068,32 +2206,32 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
         <v>-100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K32" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>100</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2112,8 +2250,14 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2133,25 +2277,25 @@
         <v>0</v>
       </c>
       <c r="I33" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
         <v>700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-100</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-400</v>
       </c>
       <c r="N33" s="3">
         <v>-100</v>
       </c>
       <c r="O33" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="P33" s="3">
         <v>-100</v>
@@ -2160,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="R33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S33" s="3">
         <v>0</v>
@@ -2171,8 +2315,14 @@
       <c r="U33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2230,8 +2380,14 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2251,25 +2407,25 @@
         <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
         <v>700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-100</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-400</v>
       </c>
       <c r="N35" s="3">
         <v>-100</v>
       </c>
       <c r="O35" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="P35" s="3">
         <v>-100</v>
@@ -2278,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="R35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S35" s="3">
         <v>0</v>
@@ -2289,72 +2445,84 @@
       <c r="U35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44377</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>43434</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43343</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43251</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43159</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43069</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>42978</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>42886</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>42794</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42704</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42613</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42521</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2376,8 +2544,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2399,8 +2569,10 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2422,8 +2594,8 @@
       <c r="I41" s="3">
         <v>0</v>
       </c>
-      <c r="J41" s="3">
-        <v>0</v>
+      <c r="J41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K41" s="3">
         <v>0</v>
@@ -2441,13 +2613,13 @@
         <v>0</v>
       </c>
       <c r="P41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q41" s="3">
         <v>0</v>
       </c>
       <c r="R41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S41" s="3">
         <v>0</v>
@@ -2458,8 +2630,14 @@
       <c r="U41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3">
+        <v>0</v>
+      </c>
+      <c r="W41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2505,11 +2683,11 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>4</v>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>4</v>
@@ -2517,8 +2695,14 @@
       <c r="U42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2532,13 +2716,13 @@
         <v>100</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="H43" s="3">
+        <v>100</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
@@ -2555,11 +2739,11 @@
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2576,8 +2760,14 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2635,8 +2825,14 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2658,8 +2854,8 @@
       <c r="I45" s="3">
         <v>0</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2679,11 +2875,11 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>4</v>
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
+        <v>0</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>4</v>
@@ -2694,8 +2890,14 @@
       <c r="U45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2712,13 +2914,13 @@
         <v>100</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2736,13 +2938,13 @@
         <v>0</v>
       </c>
       <c r="P46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
       <c r="R46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S46" s="3">
         <v>0</v>
@@ -2753,8 +2955,14 @@
       <c r="U46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2767,11 +2975,11 @@
       <c r="F47" s="3">
         <v>700</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>4</v>
+      <c r="G47" s="3">
+        <v>700</v>
+      </c>
+      <c r="H47" s="3">
+        <v>700</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>4</v>
@@ -2782,11 +2990,11 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2812,8 +3020,14 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2835,8 +3049,8 @@
       <c r="I48" s="3">
         <v>0</v>
       </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="J48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -2845,19 +3059,19 @@
         <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3">
         <v>100</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
+      <c r="P48" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>100</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>4</v>
@@ -2871,13 +3085,19 @@
       <c r="U48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="E49" s="3">
         <v>3000</v>
@@ -2886,14 +3106,14 @@
         <v>3000</v>
       </c>
       <c r="G49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I49" s="3">
         <v>2900</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2909,11 +3129,11 @@
       <c r="N49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -2930,8 +3150,14 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2989,8 +3215,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3048,8 +3280,14 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3059,20 +3297,20 @@
       <c r="E52" s="3">
         <v>0</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3107,8 +3345,14 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3166,31 +3410,37 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="E54" s="3">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="F54" s="3">
         <v>3700</v>
       </c>
       <c r="G54" s="3">
+        <v>3700</v>
+      </c>
+      <c r="H54" s="3">
+        <v>3700</v>
+      </c>
+      <c r="I54" s="3">
         <v>3000</v>
       </c>
-      <c r="H54" s="3">
-        <v>0</v>
-      </c>
-      <c r="I54" s="3">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3">
-        <v>0</v>
+      <c r="J54" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K54" s="3">
         <v>0</v>
@@ -3199,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="M54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O54" s="3">
         <v>100</v>
@@ -3211,10 +3461,10 @@
         <v>100</v>
       </c>
       <c r="Q54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S54" s="3">
         <v>0</v>
@@ -3225,8 +3475,14 @@
       <c r="U54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3">
+        <v>0</v>
+      </c>
+      <c r="W54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3248,8 +3504,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3271,31 +3529,33 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3">
-        <v>200</v>
-      </c>
-      <c r="I57" s="3">
-        <v>100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>100</v>
+      <c r="J57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
@@ -3304,10 +3564,10 @@
         <v>100</v>
       </c>
       <c r="M57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O57" s="3">
         <v>0</v>
@@ -3330,8 +3590,14 @@
       <c r="U57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3345,28 +3611,28 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>200</v>
       </c>
-      <c r="H58" s="3">
-        <v>400</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K58" s="3">
         <v>600</v>
-      </c>
-      <c r="J58" s="3">
-        <v>500</v>
-      </c>
-      <c r="K58" s="3">
-        <v>500</v>
       </c>
       <c r="L58" s="3">
         <v>500</v>
       </c>
       <c r="M58" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="N58" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="O58" s="3">
         <v>100</v>
@@ -3374,11 +3640,11 @@
       <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
+      <c r="Q58" s="3">
+        <v>100</v>
+      </c>
+      <c r="R58" s="3">
+        <v>100</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>4</v>
@@ -3389,31 +3655,37 @@
       <c r="U58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="E59" s="3">
         <v>700</v>
       </c>
       <c r="F59" s="3">
+        <v>700</v>
+      </c>
+      <c r="G59" s="3">
+        <v>700</v>
+      </c>
+      <c r="H59" s="3">
         <v>800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>600</v>
       </c>
-      <c r="H59" s="3">
-        <v>200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>100</v>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K59" s="3">
         <v>100</v>
@@ -3448,55 +3720,61 @@
       <c r="U59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3">
+        <v>100</v>
+      </c>
+      <c r="W59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F60" s="3">
         <v>1900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K60" s="3">
         <v>800</v>
       </c>
-      <c r="I60" s="3">
-        <v>800</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>300</v>
-      </c>
-      <c r="N60" s="3">
-        <v>200</v>
-      </c>
-      <c r="O60" s="3">
-        <v>200</v>
       </c>
       <c r="P60" s="3">
         <v>200</v>
       </c>
       <c r="Q60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S60" s="3">
         <v>100</v>
@@ -3507,29 +3785,35 @@
       <c r="U60" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3">
+        <v>100</v>
+      </c>
+      <c r="W60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F61" s="3">
         <v>1600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1800</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -3566,8 +3850,14 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3625,8 +3915,14 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3684,8 +3980,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3743,8 +4045,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3802,55 +4110,61 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="E66" s="3">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="F66" s="3">
         <v>3500</v>
       </c>
       <c r="G66" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H66" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I66" s="3">
         <v>3100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K66" s="3">
         <v>800</v>
       </c>
-      <c r="I66" s="3">
-        <v>800</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>300</v>
-      </c>
-      <c r="N66" s="3">
-        <v>200</v>
-      </c>
-      <c r="O66" s="3">
-        <v>200</v>
       </c>
       <c r="P66" s="3">
         <v>200</v>
       </c>
       <c r="Q66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S66" s="3">
         <v>100</v>
@@ -3861,8 +4175,14 @@
       <c r="U66" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3">
+        <v>100</v>
+      </c>
+      <c r="W66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3884,8 +4204,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3943,8 +4265,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4002,16 +4330,22 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="E70" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="F70" s="3">
         <v>900</v>
@@ -4020,10 +4354,10 @@
         <v>900</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -4061,8 +4395,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4120,8 +4460,14 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4132,43 +4478,43 @@
         <v>-2400</v>
       </c>
       <c r="F72" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="H72" s="3">
         <v>-2300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-2100</v>
       </c>
-      <c r="H72" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-1200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-1100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-1100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-700</v>
-      </c>
-      <c r="N72" s="3">
-        <v>-600</v>
-      </c>
-      <c r="O72" s="3">
-        <v>-600</v>
       </c>
       <c r="P72" s="3">
         <v>-600</v>
       </c>
       <c r="Q72" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="R72" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="S72" s="3">
         <v>-500</v>
@@ -4179,8 +4525,14 @@
       <c r="U72" s="3">
         <v>-500</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W72" s="3">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4238,8 +4590,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4297,8 +4655,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4356,46 +4720,52 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-600</v>
+        <v>-900</v>
       </c>
       <c r="E76" s="3">
-        <v>-600</v>
+        <v>-900</v>
       </c>
       <c r="F76" s="3">
         <v>-600</v>
       </c>
       <c r="G76" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H76" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I76" s="3">
         <v>-1000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K76" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L76" s="3">
         <v>-700</v>
       </c>
-      <c r="I76" s="3">
-        <v>-800</v>
-      </c>
-      <c r="J76" s="3">
-        <v>-700</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-200</v>
-      </c>
-      <c r="N76" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O76" s="3">
-        <v>-100</v>
       </c>
       <c r="P76" s="3">
         <v>-100</v>
@@ -4415,8 +4785,14 @@
       <c r="U76" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W76" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4474,72 +4850,84 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44377</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>43434</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43343</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43251</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43159</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43069</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>42978</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>42886</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>42794</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42704</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42613</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42521</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4559,25 +4947,25 @@
         <v>0</v>
       </c>
       <c r="I81" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3">
         <v>700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-100</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-400</v>
       </c>
       <c r="N81" s="3">
         <v>-100</v>
       </c>
       <c r="O81" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="P81" s="3">
         <v>-100</v>
@@ -4586,7 +4974,7 @@
         <v>0</v>
       </c>
       <c r="R81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S81" s="3">
         <v>0</v>
@@ -4597,8 +4985,14 @@
       <c r="U81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4620,8 +5014,10 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4632,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
         <v>0</v>
@@ -4643,17 +5039,17 @@
       <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
+        <v>100</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -4679,8 +5075,14 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4738,8 +5140,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4797,8 +5205,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4856,8 +5270,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4915,8 +5335,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4974,8 +5400,14 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4983,10 +5415,10 @@
         <v>0</v>
       </c>
       <c r="E89" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="F89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G89" s="3">
         <v>100</v>
@@ -4995,25 +5427,25 @@
         <v>100</v>
       </c>
       <c r="I89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J89" s="3">
         <v>100</v>
       </c>
       <c r="K89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L89" s="3">
+        <v>100</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
         <v>300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-200</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O89" s="3">
-        <v>0</v>
       </c>
       <c r="P89" s="3">
         <v>-100</v>
@@ -5022,7 +5454,7 @@
         <v>0</v>
       </c>
       <c r="R89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S89" s="3">
         <v>0</v>
@@ -5033,8 +5465,14 @@
       <c r="U89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5056,8 +5494,10 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5085,14 +5525,14 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>4</v>
+      <c r="L91" s="3">
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="N91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -5115,8 +5555,14 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5174,8 +5620,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5233,8 +5685,14 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5257,16 +5715,16 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>100</v>
-      </c>
       <c r="M94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N94" s="3">
         <v>100</v>
@@ -5275,25 +5733,31 @@
         <v>-100</v>
       </c>
       <c r="P94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5315,8 +5779,10 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5374,8 +5840,14 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5433,8 +5905,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5492,8 +5970,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5551,8 +6035,14 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5560,10 +6050,10 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3">
         <v>-100</v>
@@ -5572,35 +6062,35 @@
         <v>-100</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>4</v>
       </c>
@@ -5610,8 +6100,14 @@
       <c r="U100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5669,8 +6165,14 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5690,34 +6192,34 @@
         <v>0</v>
       </c>
       <c r="I102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
       <c r="K102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S102" s="3">
         <v>0</v>
@@ -5726,6 +6228,12 @@
         <v>0</v>
       </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ATVK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATVK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
   <si>
     <t>ATVK</t>
   </si>
@@ -656,106 +656,110 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43434</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43343</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43251</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43159</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43069</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42978</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42886</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>42794</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>42704</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>42613</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>42521</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -769,26 +773,26 @@
         <v>200</v>
       </c>
       <c r="G8" s="3">
+        <v>200</v>
+      </c>
+      <c r="H8" s="3">
         <v>300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>200</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
@@ -819,8 +823,11 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -884,8 +891,11 @@
       <c r="W9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -949,8 +959,11 @@
       <c r="W10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,8 +1121,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1133,12 +1153,12 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>-800</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1148,8 +1168,8 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1169,8 +1189,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1187,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
         <v>100</v>
@@ -1199,10 +1222,10 @@
         <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>4</v>
@@ -1210,8 +1233,8 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,13 +1282,14 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E17" s="3">
         <v>200</v>
@@ -1271,43 +1298,43 @@
         <v>200</v>
       </c>
       <c r="G17" s="3">
+        <v>200</v>
+      </c>
+      <c r="H17" s="3">
         <v>300</v>
-      </c>
-      <c r="H17" s="3">
-        <v>200</v>
       </c>
       <c r="I17" s="3">
         <v>200</v>
       </c>
       <c r="J17" s="3">
+        <v>200</v>
+      </c>
+      <c r="K17" s="3">
         <v>700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>-500</v>
       </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
       <c r="N17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O17" s="3">
+        <v>100</v>
+      </c>
+      <c r="P17" s="3">
         <v>200</v>
       </c>
-      <c r="P17" s="3">
-        <v>100</v>
-      </c>
       <c r="Q17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T17" s="3">
         <v>0</v>
@@ -1321,13 +1348,16 @@
       <c r="W17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
@@ -1342,38 +1372,38 @@
         <v>0</v>
       </c>
       <c r="I18" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="K18" s="3">
         <v>-100</v>
       </c>
       <c r="L18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M18" s="3">
         <v>700</v>
       </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
       <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
         <v>-100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-100</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
       <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
       <c r="T18" s="3">
         <v>0</v>
       </c>
@@ -1386,8 +1416,11 @@
       <c r="W18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,8 +1444,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1432,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>100</v>
@@ -1441,20 +1475,20 @@
         <v>100</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1476,8 +1510,11 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1488,25 +1525,25 @@
         <v>100</v>
       </c>
       <c r="F21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21" s="3">
         <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
+        <v>100</v>
+      </c>
+      <c r="J21" s="3">
         <v>300</v>
       </c>
-      <c r="J21" s="3">
-        <v>100</v>
-      </c>
       <c r="K21" s="3">
         <v>100</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
+      <c r="L21" s="3">
+        <v>100</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
@@ -1541,8 +1578,11 @@
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1550,10 +1590,10 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -1573,8 +1613,8 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>4</v>
@@ -1585,8 +1625,8 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1606,8 +1646,11 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1627,38 +1670,38 @@
         <v>0</v>
       </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>200</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
       <c r="K23" s="3">
         <v>0</v>
       </c>
       <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
         <v>700</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-100</v>
       </c>
       <c r="N23" s="3">
         <v>-100</v>
       </c>
       <c r="O23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P23" s="3">
         <v>-400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-100</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
         <v>0</v>
       </c>
@@ -1671,8 +1714,11 @@
       <c r="W23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1736,8 +1782,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,8 +1850,11 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1822,38 +1874,38 @@
         <v>0</v>
       </c>
       <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>200</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
       <c r="K26" s="3">
         <v>0</v>
       </c>
       <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
         <v>700</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-100</v>
       </c>
       <c r="N26" s="3">
         <v>-100</v>
       </c>
       <c r="O26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P26" s="3">
         <v>-400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
         <v>0</v>
       </c>
@@ -1866,8 +1918,11 @@
       <c r="W26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1887,38 +1942,38 @@
         <v>0</v>
       </c>
       <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>200</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
       <c r="K27" s="3">
         <v>0</v>
       </c>
       <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
         <v>700</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-100</v>
       </c>
       <c r="N27" s="3">
         <v>-100</v>
       </c>
       <c r="O27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P27" s="3">
         <v>-400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
         <v>0</v>
       </c>
@@ -1931,8 +1986,11 @@
       <c r="W27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,8 +2258,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2212,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>-100</v>
@@ -2221,20 +2291,20 @@
         <v>-100</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2256,8 +2326,11 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2277,38 +2350,38 @@
         <v>0</v>
       </c>
       <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>200</v>
       </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
       <c r="K33" s="3">
         <v>0</v>
       </c>
       <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
         <v>700</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-100</v>
       </c>
       <c r="N33" s="3">
         <v>-100</v>
       </c>
       <c r="O33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P33" s="3">
         <v>-400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
         <v>0</v>
       </c>
@@ -2321,8 +2394,11 @@
       <c r="W33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,8 +2462,11 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2407,38 +2486,38 @@
         <v>0</v>
       </c>
       <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>200</v>
       </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
       <c r="K35" s="3">
         <v>0</v>
       </c>
       <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
         <v>700</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-100</v>
       </c>
       <c r="N35" s="3">
         <v>-100</v>
       </c>
       <c r="O35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P35" s="3">
         <v>-400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
         <v>0</v>
       </c>
@@ -2451,78 +2530,84 @@
       <c r="W35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43434</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43343</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43251</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43159</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43069</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42978</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42886</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>42794</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>42704</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>42613</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>42521</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,8 +2657,9 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2594,11 +2681,11 @@
       <c r="I41" s="3">
         <v>0</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K41" s="3">
-        <v>0</v>
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L41" s="3">
         <v>0</v>
@@ -2619,10 +2706,10 @@
         <v>0</v>
       </c>
       <c r="R41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T41" s="3">
         <v>0</v>
@@ -2636,8 +2723,11 @@
       <c r="W41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2689,8 +2779,8 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>4</v>
+      <c r="T42" s="3">
+        <v>0</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>4</v>
@@ -2701,8 +2791,11 @@
       <c r="W42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2722,10 +2815,10 @@
         <v>100</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="J43" s="3">
+        <v>0</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
@@ -2745,8 +2838,8 @@
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -2766,8 +2859,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2831,8 +2927,11 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2854,11 +2953,11 @@
       <c r="I45" s="3">
         <v>0</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -2881,8 +2980,8 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>4</v>
+      <c r="S45" s="3">
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>4</v>
@@ -2896,8 +2995,11 @@
       <c r="W45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2919,11 +3021,11 @@
       <c r="I46" s="3">
         <v>100</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K46" s="3">
-        <v>0</v>
+      <c r="J46" s="3">
+        <v>100</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L46" s="3">
         <v>0</v>
@@ -2944,10 +3046,10 @@
         <v>0</v>
       </c>
       <c r="R46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T46" s="3">
         <v>0</v>
@@ -2961,8 +3063,11 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2981,8 +3086,8 @@
       <c r="H47" s="3">
         <v>700</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
+      <c r="I47" s="3">
+        <v>700</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>4</v>
@@ -2996,8 +3101,8 @@
       <c r="M47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -3026,8 +3131,11 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3049,11 +3157,11 @@
       <c r="I48" s="3">
         <v>0</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="J48" s="3">
+        <v>0</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -3065,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="O48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3">
         <v>100</v>
@@ -3073,8 +3181,8 @@
       <c r="Q48" s="3">
         <v>100</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>4</v>
+      <c r="R48" s="3">
+        <v>100</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>4</v>
@@ -3091,8 +3199,11 @@
       <c r="W48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3100,7 +3211,7 @@
         <v>2900</v>
       </c>
       <c r="E49" s="3">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="F49" s="3">
         <v>3000</v>
@@ -3112,11 +3223,11 @@
         <v>3000</v>
       </c>
       <c r="I49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J49" s="3">
         <v>2900</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3135,8 +3246,8 @@
       <c r="P49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,8 +3403,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3297,8 +3417,8 @@
       <c r="E52" s="3">
         <v>0</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
+      <c r="F52" s="3">
+        <v>0</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>4</v>
@@ -3312,8 +3432,8 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,19 +3539,22 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="E54" s="3">
         <v>3800</v>
       </c>
       <c r="F54" s="3">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="G54" s="3">
         <v>3700</v>
@@ -3437,13 +3563,13 @@
         <v>3700</v>
       </c>
       <c r="I54" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J54" s="3">
         <v>3000</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K54" s="3">
-        <v>0</v>
+      <c r="K54" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L54" s="3">
         <v>0</v>
@@ -3455,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="O54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P54" s="3">
         <v>100</v>
@@ -3467,7 +3593,7 @@
         <v>100</v>
       </c>
       <c r="S54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T54" s="3">
         <v>0</v>
@@ -3481,8 +3607,11 @@
       <c r="W54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,8 +3661,9 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3540,25 +3671,25 @@
         <v>600</v>
       </c>
       <c r="E57" s="3">
+        <v>600</v>
+      </c>
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K57" s="3">
-        <v>100</v>
+      <c r="K57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L57" s="3">
         <v>100</v>
@@ -3570,7 +3701,7 @@
         <v>100</v>
       </c>
       <c r="O57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
@@ -3596,8 +3727,11 @@
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3617,16 +3751,16 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>200</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="K58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L58" s="3">
         <v>600</v>
-      </c>
-      <c r="L58" s="3">
-        <v>500</v>
       </c>
       <c r="M58" s="3">
         <v>500</v>
@@ -3635,7 +3769,7 @@
         <v>500</v>
       </c>
       <c r="O58" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="P58" s="3">
         <v>100</v>
@@ -3646,8 +3780,8 @@
       <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
+      <c r="S58" s="3">
+        <v>100</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>4</v>
@@ -3661,16 +3795,19 @@
       <c r="W58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>700</v>
       </c>
       <c r="F59" s="3">
         <v>700</v>
@@ -3679,16 +3816,16 @@
         <v>700</v>
       </c>
       <c r="H59" s="3">
+        <v>700</v>
+      </c>
+      <c r="I59" s="3">
         <v>800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>600</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K59" s="3">
-        <v>100</v>
+      <c r="K59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L59" s="3">
         <v>100</v>
@@ -3726,49 +3863,52 @@
       <c r="W59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1700</v>
-      </c>
-      <c r="F60" s="3">
-        <v>1900</v>
       </c>
       <c r="G60" s="3">
         <v>1900</v>
       </c>
       <c r="H60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I60" s="3">
         <v>1800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1300</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L60" s="3">
         <v>800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>700</v>
-      </c>
-      <c r="M60" s="3">
-        <v>600</v>
       </c>
       <c r="N60" s="3">
         <v>600</v>
       </c>
       <c r="O60" s="3">
+        <v>600</v>
+      </c>
+      <c r="P60" s="3">
         <v>300</v>
-      </c>
-      <c r="P60" s="3">
-        <v>200</v>
       </c>
       <c r="Q60" s="3">
         <v>200</v>
@@ -3777,7 +3917,7 @@
         <v>200</v>
       </c>
       <c r="S60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T60" s="3">
         <v>100</v>
@@ -3791,8 +3931,11 @@
       <c r="W60" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3800,23 +3943,23 @@
         <v>2000</v>
       </c>
       <c r="E61" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F61" s="3">
         <v>1900</v>
-      </c>
-      <c r="F61" s="3">
-        <v>1600</v>
       </c>
       <c r="G61" s="3">
         <v>1600</v>
       </c>
       <c r="H61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I61" s="3">
         <v>1700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1800</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -3856,8 +3999,11 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,19 +4271,22 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="E66" s="3">
         <v>3600</v>
       </c>
       <c r="F66" s="3">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="G66" s="3">
         <v>3500</v>
@@ -4137,28 +4295,28 @@
         <v>3500</v>
       </c>
       <c r="I66" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J66" s="3">
         <v>3100</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3">
         <v>800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>700</v>
-      </c>
-      <c r="M66" s="3">
-        <v>600</v>
       </c>
       <c r="N66" s="3">
         <v>600</v>
       </c>
       <c r="O66" s="3">
+        <v>600</v>
+      </c>
+      <c r="P66" s="3">
         <v>300</v>
-      </c>
-      <c r="P66" s="3">
-        <v>200</v>
       </c>
       <c r="Q66" s="3">
         <v>200</v>
@@ -4167,7 +4325,7 @@
         <v>200</v>
       </c>
       <c r="S66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T66" s="3">
         <v>100</v>
@@ -4181,8 +4339,11 @@
       <c r="W66" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4348,7 +4516,7 @@
         <v>1100</v>
       </c>
       <c r="F70" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="G70" s="3">
         <v>900</v>
@@ -4360,7 +4528,7 @@
         <v>900</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,8 +4637,11 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4484,31 +4658,31 @@
         <v>-2400</v>
       </c>
       <c r="H72" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="I72" s="3">
         <v>-2300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2100</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>-1300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1200</v>
-      </c>
-      <c r="M72" s="3">
-        <v>-1100</v>
       </c>
       <c r="N72" s="3">
         <v>-1100</v>
       </c>
       <c r="O72" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="P72" s="3">
         <v>-700</v>
-      </c>
-      <c r="P72" s="3">
-        <v>-600</v>
       </c>
       <c r="Q72" s="3">
         <v>-600</v>
@@ -4517,7 +4691,7 @@
         <v>-600</v>
       </c>
       <c r="S72" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="T72" s="3">
         <v>-500</v>
@@ -4531,8 +4705,11 @@
       <c r="W72" s="3">
         <v>-500</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,8 +4909,11 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -4738,7 +4924,7 @@
         <v>-900</v>
       </c>
       <c r="F76" s="3">
-        <v>-600</v>
+        <v>-900</v>
       </c>
       <c r="G76" s="3">
         <v>-600</v>
@@ -4747,28 +4933,28 @@
         <v>-600</v>
       </c>
       <c r="I76" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J76" s="3">
         <v>-1000</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L76" s="3">
         <v>-800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-700</v>
-      </c>
-      <c r="M76" s="3">
-        <v>-600</v>
       </c>
       <c r="N76" s="3">
         <v>-600</v>
       </c>
       <c r="O76" s="3">
+        <v>-600</v>
+      </c>
+      <c r="P76" s="3">
         <v>-200</v>
-      </c>
-      <c r="P76" s="3">
-        <v>-100</v>
       </c>
       <c r="Q76" s="3">
         <v>-100</v>
@@ -4791,8 +4977,11 @@
       <c r="W76" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,78 +5045,84 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43434</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43343</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43251</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43159</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43069</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42978</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42886</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>42794</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>42704</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>42613</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>42521</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4947,38 +5142,38 @@
         <v>0</v>
       </c>
       <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>200</v>
       </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
       <c r="K81" s="3">
         <v>0</v>
       </c>
       <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
         <v>700</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-100</v>
       </c>
       <c r="N81" s="3">
         <v>-100</v>
       </c>
       <c r="O81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P81" s="3">
         <v>-400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
         <v>0</v>
       </c>
@@ -4991,8 +5186,11 @@
       <c r="W81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,8 +5214,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5034,25 +5233,25 @@
         <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
-        <v>100</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
+        <v>100</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -5081,8 +5280,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,8 +5620,11 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5415,22 +5632,22 @@
         <v>0</v>
       </c>
       <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>-200</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
       <c r="G89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H89" s="3">
         <v>100</v>
       </c>
       <c r="I89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K89" s="3">
         <v>100</v>
@@ -5439,26 +5656,26 @@
         <v>100</v>
       </c>
       <c r="M89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
         <v>300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-100</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
         <v>0</v>
       </c>
@@ -5471,8 +5688,11 @@
       <c r="W89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,8 +5716,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5531,11 +5752,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -5561,8 +5782,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,8 +5918,11 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5721,43 +5951,46 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>100</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>100</v>
-      </c>
       <c r="Q94" s="3">
+        <v>100</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,8 +6284,11 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6050,50 +6296,50 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3">
         <v>-100</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K100" s="3">
         <v>-100</v>
       </c>
       <c r="L100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>300</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>4</v>
       </c>
@@ -6106,8 +6352,11 @@
       <c r="W100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6171,8 +6420,11 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6198,31 +6450,31 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
         <v>0</v>
       </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
-        <v>100</v>
-      </c>
       <c r="S102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T102" s="3">
         <v>0</v>
@@ -6234,6 +6486,9 @@
         <v>0</v>
       </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ATVK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATVK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
   <si>
     <t>ATVK</t>
   </si>
@@ -656,70 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>4</v>
@@ -731,16 +738,22 @@
         <v>4</v>
       </c>
       <c r="I8" s="3">
-        <v>200</v>
-      </c>
-      <c r="J8" s="3">
-        <v>200</v>
+        <v>700</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3">
+        <v>200</v>
+      </c>
+      <c r="M8" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -768,16 +781,22 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>4</v>
@@ -789,16 +808,22 @@
         <v>4</v>
       </c>
       <c r="I10" s="3">
-        <v>200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>200</v>
+        <v>700</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K10" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3">
+        <v>200</v>
+      </c>
+      <c r="M10" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,8 +835,10 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -821,17 +848,17 @@
       <c r="E12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
+      <c r="F12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3">
         <v>100</v>
@@ -839,8 +866,14 @@
       <c r="K12" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3">
+        <v>100</v>
+      </c>
+      <c r="M12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -868,28 +901,34 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F14" s="3">
         <v>-5300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-1700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>9000</v>
       </c>
-      <c r="G14" s="3">
-        <v>-4400</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
+      <c r="I14" s="3">
+        <v>-13500</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
@@ -897,8 +936,14 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -926,8 +971,14 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -936,8 +987,10 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -945,28 +998,34 @@
         <v>0</v>
       </c>
       <c r="E17" s="3">
+        <v>400</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
         <v>200</v>
       </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
       <c r="H17" s="3">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
         <v>100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -974,28 +1033,34 @@
         <v>0</v>
       </c>
       <c r="E18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
         <v>-200</v>
       </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
       <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>700</v>
+      </c>
+      <c r="J18" s="3">
         <v>-100</v>
       </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
         <v>100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1007,37 +1072,45 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3">
+        <v>700</v>
+      </c>
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1045,19 +1118,19 @@
         <v>0</v>
       </c>
       <c r="E21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
         <v>-200</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
       <c r="H21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
         <v>100</v>
@@ -1065,8 +1138,14 @@
       <c r="K21" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3">
+        <v>100</v>
+      </c>
+      <c r="M21" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1092,39 +1171,51 @@
         <v>0</v>
       </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F23" s="3">
         <v>5300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-9100</v>
       </c>
-      <c r="G23" s="3">
-        <v>4400</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>13400</v>
+      </c>
+      <c r="J23" s="3">
         <v>100</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
       <c r="K23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1152,8 +1243,14 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1181,66 +1278,84 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F26" s="3">
         <v>5300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-9100</v>
       </c>
-      <c r="G26" s="3">
-        <v>4400</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>13400</v>
+      </c>
+      <c r="J26" s="3">
         <v>100</v>
       </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
       <c r="K26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F27" s="3">
         <v>5300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-9100</v>
       </c>
-      <c r="G27" s="3">
-        <v>4400</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>13400</v>
+      </c>
+      <c r="J27" s="3">
         <v>100</v>
       </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
       <c r="K27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1268,8 +1383,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1297,8 +1418,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1326,8 +1453,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1355,66 +1488,84 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F33" s="3">
         <v>5300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-9100</v>
       </c>
-      <c r="G33" s="3">
-        <v>4400</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>13400</v>
+      </c>
+      <c r="J33" s="3">
         <v>100</v>
       </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
       <c r="K33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1442,71 +1593,89 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F35" s="3">
         <v>5300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-9100</v>
       </c>
-      <c r="G35" s="3">
-        <v>4400</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>13400</v>
+      </c>
+      <c r="J35" s="3">
         <v>100</v>
       </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
       <c r="K35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1518,8 +1687,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1531,8 +1702,10 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1545,14 +1718,14 @@
       <c r="F41" s="3">
         <v>0</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>4</v>
+      <c r="G41" s="3">
+        <v>0</v>
       </c>
       <c r="H41" s="3">
         <v>0</v>
       </c>
-      <c r="I41" s="3">
-        <v>0</v>
+      <c r="I41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J41" s="3">
         <v>0</v>
@@ -1560,8 +1733,14 @@
       <c r="K41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1589,13 +1768,19 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
+      <c r="D43" s="3">
+        <v>0</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>4</v>
@@ -1606,11 +1791,11 @@
       <c r="G43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H43" s="3">
-        <v>100</v>
-      </c>
-      <c r="I43" s="3">
-        <v>100</v>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J43" s="3">
         <v>100</v>
@@ -1618,8 +1803,14 @@
       <c r="K43" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3">
+        <v>100</v>
+      </c>
+      <c r="M43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1647,8 +1838,14 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1676,8 +1873,14 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -1690,14 +1893,14 @@
       <c r="F46" s="3">
         <v>0</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>4</v>
+      <c r="G46" s="3">
+        <v>0</v>
       </c>
       <c r="H46" s="3">
-        <v>100</v>
-      </c>
-      <c r="I46" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J46" s="3">
         <v>100</v>
@@ -1705,28 +1908,34 @@
       <c r="K46" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3">
+        <v>100</v>
+      </c>
+      <c r="M46" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F47" s="3">
         <v>12100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>6800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>5000</v>
       </c>
-      <c r="G47" s="3">
-        <v>5000</v>
-      </c>
-      <c r="H47" s="3">
-        <v>700</v>
-      </c>
       <c r="I47" s="3">
-        <v>700</v>
+        <v>14100</v>
       </c>
       <c r="J47" s="3">
         <v>700</v>
@@ -1734,45 +1943,57 @@
       <c r="K47" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>700</v>
+      </c>
+      <c r="M47" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>700</v>
+      </c>
+      <c r="E48" s="3">
         <v>400</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>4</v>
+      <c r="F48" s="3">
+        <v>400</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H48" s="3">
-        <v>0</v>
+      <c r="H48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="J48" s="3">
+        <v>0</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>2000</v>
@@ -1781,10 +2002,10 @@
         <v>2000</v>
       </c>
       <c r="H49" s="3">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="I49" s="3">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="J49" s="3">
         <v>2400</v>
@@ -1792,8 +2013,14 @@
       <c r="K49" s="3">
         <v>2400</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="M49" s="3">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1821,8 +2048,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1850,8 +2083,14 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -1859,10 +2098,10 @@
         <v>100</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
@@ -1879,8 +2118,14 @@
       <c r="K52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1908,37 +2153,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F54" s="3">
         <v>14800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>8900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>7200</v>
       </c>
-      <c r="G54" s="3">
-        <v>7200</v>
-      </c>
-      <c r="H54" s="3">
-        <v>3800</v>
-      </c>
       <c r="I54" s="3">
-        <v>3700</v>
+        <v>16200</v>
       </c>
       <c r="J54" s="3">
         <v>3800</v>
       </c>
       <c r="K54" s="3">
+        <v>3700</v>
+      </c>
+      <c r="L54" s="3">
         <v>3800</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M54" s="3">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1950,8 +2207,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1963,8 +2222,10 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -1981,27 +2242,33 @@
         <v>500</v>
       </c>
       <c r="H57" s="3">
+        <v>500</v>
+      </c>
+      <c r="I57" s="3">
+        <v>500</v>
+      </c>
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -2021,74 +2288,92 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E59" s="3">
         <v>900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
+        <v>900</v>
+      </c>
+      <c r="G59" s="3">
         <v>300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>300</v>
-      </c>
-      <c r="G59" s="3">
-        <v>900</v>
-      </c>
-      <c r="H59" s="3">
-        <v>600</v>
       </c>
       <c r="I59" s="3">
         <v>300</v>
       </c>
       <c r="J59" s="3">
+        <v>600</v>
+      </c>
+      <c r="K59" s="3">
+        <v>300</v>
+      </c>
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F60" s="3">
         <v>2100</v>
-      </c>
-      <c r="E60" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F60" s="3">
-        <v>1500</v>
       </c>
       <c r="G60" s="3">
         <v>1500</v>
       </c>
       <c r="H60" s="3">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I60" s="3">
         <v>1500</v>
       </c>
       <c r="J60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L60" s="3">
         <v>1600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E61" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="F61" s="3">
         <v>1000</v>
@@ -2097,33 +2382,39 @@
         <v>1000</v>
       </c>
       <c r="H61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J61" s="3">
         <v>1600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
+      <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
+      <c r="G62" s="3">
+        <v>0</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>4</v>
@@ -2137,8 +2428,14 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2166,8 +2463,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2195,8 +2498,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2224,37 +2533,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F66" s="3">
         <v>3100</v>
-      </c>
-      <c r="E66" s="3">
-        <v>2500</v>
-      </c>
-      <c r="F66" s="3">
-        <v>2500</v>
       </c>
       <c r="G66" s="3">
         <v>2500</v>
       </c>
       <c r="H66" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I66" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J66" s="3">
         <v>3500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2266,8 +2587,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2295,8 +2618,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2324,8 +2653,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2353,8 +2688,14 @@
       <c r="K70" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M70" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2382,37 +2723,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F72" s="3">
         <v>8900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>3600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2100</v>
       </c>
-      <c r="G72" s="3">
-        <v>2100</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
+        <v>11100</v>
+      </c>
+      <c r="J72" s="3">
         <v>-2300</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-2400</v>
       </c>
       <c r="K72" s="3">
         <v>-2400</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="M72" s="3">
+        <v>-2400</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2440,8 +2793,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2469,8 +2828,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2498,37 +2863,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F76" s="3">
         <v>10500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>5300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3600</v>
       </c>
-      <c r="G76" s="3">
-        <v>3600</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
+        <v>12600</v>
+      </c>
+      <c r="J76" s="3">
         <v>-800</v>
-      </c>
-      <c r="I76" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J76" s="3">
-        <v>-900</v>
       </c>
       <c r="K76" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M76" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2556,71 +2933,89 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F81" s="3">
         <v>5300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-9100</v>
       </c>
-      <c r="G81" s="3">
-        <v>4400</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>13400</v>
+      </c>
+      <c r="J81" s="3">
         <v>100</v>
       </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
       <c r="K81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2632,37 +3027,45 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
+      <c r="F83" s="3">
+        <v>0</v>
       </c>
       <c r="G83" s="3">
         <v>0</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I83" s="3">
-        <v>100</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2690,8 +3093,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2719,8 +3128,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2748,8 +3163,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2777,8 +3198,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2806,37 +3233,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>500</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
       <c r="G89" s="3">
         <v>0</v>
       </c>
       <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>400</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
       <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2848,20 +3287,22 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G91" s="3" t="s">
         <v>4</v>
       </c>
@@ -2877,8 +3318,14 @@
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2906,8 +3353,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2935,20 +3388,26 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G94" s="3" t="s">
         <v>4</v>
       </c>
@@ -2964,8 +3423,14 @@
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2977,8 +3442,10 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3006,8 +3473,14 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3035,8 +3508,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3064,8 +3543,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3093,37 +3578,49 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-400</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3151,8 +3648,14 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3178,6 +3681,12 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>0</v>
       </c>
     </row>
